--- a/employeedata 2.xlsx
+++ b/employeedata 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/jayalakshmi_anand_uipath_com/Documents/Documents/UiPath/My Projects/Certification practice/certificatepractice_Windows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_F25DC773A252ABDACC1048F5891A617E5ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F7DA90-83B9-40BE-8A77-66679FE79F27}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_F25DC773A252ABDACC1048F5891A617E5ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750A55F1-C8B6-40CA-B5F9-9B322E489452}"/>
   <bookViews>
-    <workbookView xWindow="-8227" yWindow="10845" windowWidth="19395" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2813" yWindow="2250" windowWidth="14400" windowHeight="7462" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -375,12 +375,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -394,7 +394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -408,7 +408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -422,7 +422,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -436,19 +436,19 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9" s="1"/>
     </row>
   </sheetData>
